--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="79">
   <si>
     <t>Property</t>
   </si>
@@ -70,19 +70,7 @@
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>ANS (https://esante.gouv.fr)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>France</t>
+    <t>Agence du numérique en santé</t>
   </si>
   <si>
     <t>Description</t>
@@ -396,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -485,88 +473,72 @@
       <c r="A11" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="B11" t="s" s="2">
-        <v>20</v>
-      </c>
+      <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>22</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>24</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B19" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>29</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -581,202 +553,202 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -791,13 +763,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -805,38 +777,38 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2024-11</t>
+    <t>2024-12</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T09:50:00+00:00</t>
+    <t>2024-12-09T15:50:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -112,7 +112,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>68514</t>
+    <t>68735</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2024-12</t>
+    <t>2025-01</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-09T15:50:00+00:00</t>
+    <t>2025-01-10T13:13:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -112,7 +112,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>68735</t>
+    <t>69231</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="81">
   <si>
     <t>Property</t>
   </si>
@@ -31,24 +31,30 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-sms</t>
+    <t>OID:2.16.840.1.113883.3.6905.2 (use: usual, )</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/#terminologie-sms (use: secondary, )</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>2025-01</t>
+    <t>2025-02</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Dictionnaire_des_substances_m_dicamenteuses__SMS_</t>
+    <t>Dictionnaire_SMS_Substance_Management_Services_</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
+    <t>Dictionnaire européen multilingue des substances entrant dans la composition de médicaments</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -64,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-10T13:13:00+00:00</t>
+    <t>2025-02-11T14:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -112,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>69231</t>
+    <t>69429</t>
   </si>
   <si>
     <t>Code</t>
@@ -384,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -417,25 +423,27 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>6</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>8</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
       </c>
-      <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -473,72 +481,80 @@
       <c r="A11" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" t="s" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B15" t="s" s="2">
         <v>24</v>
       </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" t="s" s="2">
+        <v>26</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B19" t="s" s="2">
         <v>29</v>
       </c>
+      <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="B20" s="2"/>
+      <c r="B20" t="s" s="2">
+        <v>31</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B21" t="s" s="2">
         <v>32</v>
+      </c>
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -553,202 +569,202 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="D14" t="s" s="2">
         <v>67</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>65</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="D16" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -763,13 +779,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -777,38 +793,38 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-02</t>
+    <t>2025-03</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:00:00+00:00</t>
+    <t>2025-03-10T12:15:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>69429</t>
+    <t>69477</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T12:15:00+00:00</t>
+    <t>2025-03-26T10:10:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>69477</t>
+    <t>69610</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-03</t>
+    <t>2025-04</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-26T10:10:00+00:00</t>
+    <t>2025-04-05T16:10:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>69610</t>
+    <t>69687</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="83">
   <si>
     <t>Property</t>
   </si>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <t>Agence du numérique en santé</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -390,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -489,72 +495,80 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B16" t="s" s="2">
         <v>26</v>
       </c>
+      <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
         <v>27</v>
       </c>
-      <c r="B17" s="2"/>
+      <c r="B17" t="s" s="2">
+        <v>28</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B20" t="s" s="2">
         <v>31</v>
       </c>
+      <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="B21" s="2"/>
+      <c r="B21" t="s" s="2">
+        <v>33</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B22" t="s" s="2">
         <v>34</v>
+      </c>
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -569,202 +583,202 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s" s="2">
         <v>69</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D16" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -779,13 +793,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -793,38 +807,38 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-04</t>
+    <t>2025-05</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-05T16:10:00+00:00</t>
+    <t>2025-05-07T10:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>69687</t>
+    <t>69829</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-05</t>
+    <t>2025-06</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-07T10:00:00+00:00</t>
+    <t>2025-06-04T10:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>69829</t>
+    <t>69955</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-06</t>
+    <t>2025-07</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T10:00:00+00:00</t>
+    <t>2025-07-04T11:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>69955</t>
+    <t>70056</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-07</t>
+    <t>2025-09</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T11:00:00+00:00</t>
+    <t>2025-09-08T13:13:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>70056</t>
+    <t>70429</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-11</t>
+    <t>2025-12</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-04T10:00:00+00:00</t>
+    <t>2025-12-03T10:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>70891</t>
+    <t>71032</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-12</t>
+    <t>2026-01</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T10:00:00+00:00</t>
+    <t>2026-01-08T10:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>71032</t>
+    <t>71149</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026-01</t>
+    <t>2026-02</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-08T10:00:00+00:00</t>
+    <t>2026-02-03T10:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>71149</t>
+    <t>71257</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026-02</t>
+    <t>2026-03</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:00:00+00:00</t>
+    <t>2026-03-05T10:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>71257</t>
+    <t>71486</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026-03</t>
+    <t>2026-04</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:00:00+00:00</t>
+    <t>2026-04-07T10:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>71486</t>
+    <t>71745</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026-04</t>
+    <t>2026-05</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:00:00+00:00</t>
+    <t>2026-05-05T10:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>71745</t>
+    <t>71998</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-sms.xlsx
+++ b/ig/main/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026-05</t>
+    <t>2026-06</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T10:00:00+00:00</t>
+    <t>2026-06-03T10:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>71998</t>
+    <t>72130</t>
   </si>
   <si>
     <t>Code</t>
